--- a/results/0916-all/内蒙古北部牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/内蒙古北部牧区/tech_selected_summary.xlsx
@@ -76,73 +76,73 @@
     <t>正镶白旗</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 453558.42</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>453558.42</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Increasing byproduct_beef cattle</t>
@@ -199,13 +199,13 @@
     <t>cover crop (non-leguminous)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 16569072.87</t>
+    <t>16569072.87</t>
   </si>
   <si>
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 34213.15</t>
+    <t>34213.15</t>
   </si>
 </sst>
 </file>
